--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
@@ -14761,7 +14761,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población matriculada</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:38</t>
+    <t xml:space="preserve">2026-09-07 12:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2022.xlsx
@@ -2029,7 +2029,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:56</t>
+    <t xml:space="preserve">2026-09-08 10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
